--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="3" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="782">
   <si>
     <t>方位（ほうい）</t>
   </si>
@@ -1565,6 +1565,12 @@
     <t>（决赛）</t>
   </si>
   <si>
+    <t>近道</t>
+  </si>
+  <si>
+    <t>ちかみち</t>
+  </si>
+  <si>
     <t>交通機関</t>
   </si>
   <si>
@@ -1945,6 +1951,12 @@
   </si>
   <si>
     <t>（当天往返）</t>
+  </si>
+  <si>
+    <t>改札口</t>
+  </si>
+  <si>
+    <t>かいさつぐち</t>
   </si>
   <si>
     <t>急行列車</t>
@@ -2320,6 +2332,12 @@
   </si>
   <si>
     <t>でんのう</t>
+  </si>
+  <si>
+    <t>架け橋</t>
+  </si>
+  <si>
+    <t>かけはし</t>
   </si>
   <si>
     <t>窓</t>
@@ -4292,7 +4310,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -5390,6 +5408,14 @@
       </c>
       <c r="C61" t="s">
         <v>438</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>439</v>
+      </c>
+      <c r="B62" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -5414,50 +5440,50 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>155</v>
@@ -5466,36 +5492,36 @@
         <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
@@ -5506,85 +5532,85 @@
         <v>372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
@@ -5595,85 +5621,85 @@
         <v>259</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
@@ -5684,175 +5710,181 @@
         <v>295</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C15" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C16" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J18" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:10">
+      <c r="A19" t="s">
+        <v>548</v>
+      </c>
+      <c r="B19" t="s">
+        <v>549</v>
+      </c>
       <c r="D19" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="D20" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="J20" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="D21" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="H22" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="H23" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -5875,97 +5907,97 @@
   <sheetData>
     <row r="3" ht="18" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D3" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:14">
       <c r="A4" s="4" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="N4" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:14">
       <c r="A5" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>351</v>
@@ -5974,180 +6006,186 @@
         <v>352</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D8" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E8" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F8" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="F10" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D13" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E13" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D14" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E14" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:14">
+      <c r="A15" t="s">
+        <v>643</v>
+      </c>
+      <c r="B15" t="s">
+        <v>644</v>
+      </c>
       <c r="D15" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="D16" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E16" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="F16" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -6169,80 +6207,80 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -6264,221 +6302,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B14" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -6495,246 +6533,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="J2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="B27" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>

--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="802">
   <si>
     <t>方位（ほうい）</t>
   </si>
@@ -1571,6 +1571,33 @@
     <t>ちかみち</t>
   </si>
   <si>
+    <t>屋外</t>
+  </si>
+  <si>
+    <t>おくがい</t>
+  </si>
+  <si>
+    <t>（室外）</t>
+  </si>
+  <si>
+    <t>葬式</t>
+  </si>
+  <si>
+    <t>そうしき</t>
+  </si>
+  <si>
+    <t>（葬礼）</t>
+  </si>
+  <si>
+    <t>結婚式</t>
+  </si>
+  <si>
+    <t>けっこんんしき</t>
+  </si>
+  <si>
+    <t>（婚礼）</t>
+  </si>
+  <si>
     <t>交通機関</t>
   </si>
   <si>
@@ -2039,6 +2066,15 @@
     <t>かそく</t>
   </si>
   <si>
+    <t>飛行機で…を飛び越える</t>
+  </si>
+  <si>
+    <t>とびこえる</t>
+  </si>
+  <si>
+    <t>（坐飞机飞越）</t>
+  </si>
+  <si>
     <t>木造</t>
   </si>
   <si>
@@ -2061,6 +2097,12 @@
   </si>
   <si>
     <t>しんしつ</t>
+  </si>
+  <si>
+    <t>浴室</t>
+  </si>
+  <si>
+    <t>よくしつ</t>
   </si>
   <si>
     <t>建築</t>
@@ -2191,6 +2233,12 @@
     <t>せんたくき</t>
   </si>
   <si>
+    <t>電灯</t>
+  </si>
+  <si>
+    <t>でんとう</t>
+  </si>
+  <si>
     <t>建築設備</t>
   </si>
   <si>
@@ -2212,6 +2260,12 @@
     <t>じゃぐち</t>
   </si>
   <si>
+    <t>電脳</t>
+  </si>
+  <si>
+    <t>でんのう</t>
+  </si>
+  <si>
     <t>室内</t>
   </si>
   <si>
@@ -2224,6 +2278,12 @@
     <t>しょうめいとう</t>
   </si>
   <si>
+    <t>窓</t>
+  </si>
+  <si>
+    <t>まど</t>
+  </si>
+  <si>
     <t>露天</t>
   </si>
   <si>
@@ -2237,6 +2297,15 @@
   </si>
   <si>
     <t>（廊子）</t>
+  </si>
+  <si>
+    <t>障子</t>
+  </si>
+  <si>
+    <t>しょうじ</t>
+  </si>
+  <si>
+    <t>（拉窗，拉门）</t>
   </si>
   <si>
     <t>入口</t>
@@ -2316,10 +2385,13 @@
     <t>まてんろう</t>
   </si>
   <si>
-    <t>電灯</t>
-  </si>
-  <si>
-    <t>でんとう</t>
+    <t>床の間</t>
+  </si>
+  <si>
+    <t>とこのま</t>
+  </si>
+  <si>
+    <t>（壁篭）</t>
   </si>
   <si>
     <t>工程</t>
@@ -2328,33 +2400,12 @@
     <t>（窗户）</t>
   </si>
   <si>
-    <t>電脳</t>
-  </si>
-  <si>
-    <t>でんのう</t>
-  </si>
-  <si>
     <t>架け橋</t>
   </si>
   <si>
     <t>かけはし</t>
   </si>
   <si>
-    <t>窓</t>
-  </si>
-  <si>
-    <t>まど</t>
-  </si>
-  <si>
-    <t>床の間</t>
-  </si>
-  <si>
-    <t>とこのま</t>
-  </si>
-  <si>
-    <t>（壁篭）</t>
-  </si>
-  <si>
     <t>伏見稲荷大社</t>
   </si>
   <si>
@@ -2413,6 +2464,15 @@
   </si>
   <si>
     <t>花火大会｜はなびたいかい</t>
+  </si>
+  <si>
+    <t>嵐山</t>
+  </si>
+  <si>
+    <t>あらしやま</t>
+  </si>
+  <si>
+    <t>嵐山公園｜あらしやまこうえん</t>
   </si>
   <si>
     <t>港区</t>
@@ -4310,7 +4370,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -5418,6 +5478,39 @@
         <v>440</v>
       </c>
     </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>441</v>
+      </c>
+      <c r="B63" t="s">
+        <v>442</v>
+      </c>
+      <c r="C63" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>444</v>
+      </c>
+      <c r="B64" t="s">
+        <v>445</v>
+      </c>
+      <c r="C64" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>447</v>
+      </c>
+      <c r="B65" t="s">
+        <v>448</v>
+      </c>
+      <c r="C65" t="s">
+        <v>449</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5427,7 +5520,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:L23"/>
+  <dimension ref="A2:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -5435,55 +5528,55 @@
     <col min="3" max="3" width="24.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="11.6666666666667" customWidth="1"/>
     <col min="6" max="6" width="9.55555555555556" customWidth="1"/>
-    <col min="8" max="8" width="13.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="23.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="H3" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>155</v>
@@ -5492,36 +5585,36 @@
         <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
@@ -5532,85 +5625,85 @@
         <v>372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="H6" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="H9" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
@@ -5621,85 +5714,85 @@
         <v>259</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="L10" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="L13" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
@@ -5710,181 +5803,192 @@
         <v>295</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="K14" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C15" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C16" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C17" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="J18" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="B19" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="D20" s="1" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="J20" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="D21" s="1" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="H22" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="H23" s="1" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>567</v>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="H24" t="s">
+        <v>577</v>
+      </c>
+      <c r="I24" t="s">
+        <v>578</v>
+      </c>
+      <c r="J24" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -5896,7 +6000,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:N16"/>
+  <dimension ref="A3:P15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
@@ -5905,99 +6009,105 @@
     <col min="9" max="9" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="18" spans="1:14">
+    <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="D3" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="K3" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="4" ht="18" spans="1:14">
+        <v>587</v>
+      </c>
+      <c r="O3" t="s">
+        <v>588</v>
+      </c>
+      <c r="P3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:16">
       <c r="A4" s="4" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="N4" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="5" ht="18" spans="1:14">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="5" ht="18" spans="1:16">
       <c r="A5" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="6" ht="18" spans="1:14">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>351</v>
@@ -6006,186 +6116,193 @@
         <v>352</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:14">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:14">
+        <v>623</v>
+      </c>
+      <c r="K7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L7" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="D8" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="E8" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="F8" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="9" ht="18" spans="1:14">
+        <v>632</v>
+      </c>
+      <c r="K8" t="s">
+        <v>633</v>
+      </c>
+      <c r="L8" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:14">
+        <v>638</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="F10" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="11" ht="18" spans="1:14">
+        <v>645</v>
+      </c>
+      <c r="K10" t="s">
+        <v>646</v>
+      </c>
+      <c r="L10" t="s">
+        <v>647</v>
+      </c>
+      <c r="N10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="11" ht="18" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="12" ht="18" spans="1:14">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:14">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="D13" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="E13" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:14">
+        <v>661</v>
+      </c>
+      <c r="F13" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>640</v>
-      </c>
-      <c r="D14" t="s">
-        <v>641</v>
-      </c>
-      <c r="E14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="15" ht="18" spans="1:14">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="B15" t="s">
-        <v>644</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="D16" t="s">
-        <v>647</v>
-      </c>
-      <c r="E16" t="s">
-        <v>648</v>
-      </c>
-      <c r="F16" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -6197,7 +6314,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:C10"/>
+  <dimension ref="A2:C11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -6207,80 +6324,91 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="B2" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="C2" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>669</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>687</v>
+      </c>
+      <c r="B11" t="s">
+        <v>688</v>
+      </c>
+      <c r="C11" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -6302,221 +6430,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="B3" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>677</v>
+        <v>697</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="B14" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -6533,246 +6661,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="E2" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="J2" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="B27" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>

--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="804">
   <si>
     <t>方位（ほうい）</t>
   </si>
@@ -2404,6 +2404,12 @@
   </si>
   <si>
     <t>かけはし</t>
+  </si>
+  <si>
+    <t>軒</t>
+  </si>
+  <si>
+    <t>（屋檐，房屋）</t>
   </si>
   <si>
     <t>伏見稲荷大社</t>
@@ -6293,7 +6299,10 @@
       <c r="B14" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>639</v>
+      </c>
+      <c r="E14" t="s">
         <v>664</v>
       </c>
     </row>
@@ -6303,6 +6312,12 @@
       </c>
       <c r="B15" t="s">
         <v>666</v>
+      </c>
+      <c r="D15" t="s">
+        <v>667</v>
+      </c>
+      <c r="E15" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -6324,91 +6339,91 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B11" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C11" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -6430,221 +6445,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B14" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -6661,246 +6676,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>757</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B27" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="810">
   <si>
     <t>方位（ほうい）</t>
   </si>
@@ -1419,16 +1419,22 @@
     <t>れんけい</t>
   </si>
   <si>
+    <t>送別会</t>
+  </si>
+  <si>
+    <t>そうべつかい</t>
+  </si>
+  <si>
+    <t>場合</t>
+  </si>
+  <si>
+    <t>ばあい</t>
+  </si>
+  <si>
     <t>宴会</t>
   </si>
   <si>
     <t>えんかい</t>
-  </si>
-  <si>
-    <t>場合</t>
-  </si>
-  <si>
-    <t>ばあい</t>
   </si>
   <si>
     <t>会場</t>
@@ -1458,6 +1464,12 @@
     </r>
   </si>
   <si>
+    <t>番地</t>
+  </si>
+  <si>
+    <t>ばんち</t>
+  </si>
+  <si>
     <t>物置</t>
   </si>
   <si>
@@ -1465,12 +1477,6 @@
   </si>
   <si>
     <t>置き｜おき</t>
-  </si>
-  <si>
-    <t>番地</t>
-  </si>
-  <si>
-    <t>ばんち</t>
   </si>
   <si>
     <t>首都</t>
@@ -2054,10 +2060,22 @@
     <t>びんじょう</t>
   </si>
   <si>
+    <t>私鉄</t>
+  </si>
+  <si>
+    <t>してつ</t>
+  </si>
+  <si>
     <t>減速</t>
   </si>
   <si>
     <t>げんそく</t>
+  </si>
+  <si>
+    <t>国鉄</t>
+  </si>
+  <si>
+    <t>こくてつ</t>
   </si>
   <si>
     <t>加速</t>
@@ -5338,10 +5356,10 @@
       <c r="B48" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" t="s">
         <v>402</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5352,169 +5370,175 @@
       <c r="B49" s="1" t="s">
         <v>405</v>
       </c>
+      <c r="E49" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="50" ht="18" spans="1:7">
       <c r="A50" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F50" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>413</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:7">
       <c r="A54" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:7">
       <c r="A57" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C59" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C60" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C61" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C63" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C64" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C65" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -5539,50 +5563,50 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>155</v>
@@ -5591,36 +5615,36 @@
         <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
@@ -5631,85 +5655,85 @@
         <v>372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
@@ -5720,85 +5744,85 @@
         <v>259</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L10" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L13" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
@@ -5809,192 +5833,204 @@
         <v>295</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K14" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C15" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C17" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B19" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="D20" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J20" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="D21" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
+      <c r="D22" t="s">
+        <v>575</v>
+      </c>
+      <c r="E22" t="s">
+        <v>576</v>
+      </c>
       <c r="H22" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
+      <c r="D23" t="s">
+        <v>579</v>
+      </c>
+      <c r="E23" t="s">
+        <v>580</v>
+      </c>
       <c r="H23" s="1" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="H24" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="I24" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="J24" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -6017,103 +6053,103 @@
   <sheetData>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="D3" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="K3" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="O3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="P3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="4" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="N4" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>351</v>
@@ -6122,202 +6158,202 @@
         <v>352</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="K7" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="L7" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D8" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="E8" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F8" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="K8" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="L8" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="F10" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K10" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="L10" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="N10" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D13" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E13" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="F13" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D14" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E14" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B15" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D15" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E15" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -6339,91 +6375,91 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B11" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C11" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -6445,221 +6481,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B3" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B14" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
   </sheetData>
@@ -6676,246 +6712,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E2" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="J2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="B27" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="812">
   <si>
     <t>方位（ほうい）</t>
   </si>
@@ -1464,12 +1464,24 @@
     </r>
   </si>
   <si>
+    <t>同窓会</t>
+  </si>
+  <si>
+    <t>どうそうかい</t>
+  </si>
+  <si>
     <t>番地</t>
   </si>
   <si>
     <t>ばんち</t>
   </si>
   <si>
+    <t>首都</t>
+  </si>
+  <si>
+    <t>しゅと</t>
+  </si>
+  <si>
     <t>物置</t>
   </si>
   <si>
@@ -1477,12 +1489,6 @@
   </si>
   <si>
     <t>置き｜おき</t>
-  </si>
-  <si>
-    <t>首都</t>
-  </si>
-  <si>
-    <t>しゅと</t>
   </si>
   <si>
     <t>広場</t>
@@ -5387,158 +5393,164 @@
       <c r="C50" s="5" t="s">
         <v>410</v>
       </c>
+      <c r="E50" t="s">
+        <v>411</v>
+      </c>
+      <c r="F50" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F51" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>417</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:7">
       <c r="A54" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:7">
       <c r="A57" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C59" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C60" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C61" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C63" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C64" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C65" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5563,50 +5575,50 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>155</v>
@@ -5615,36 +5627,36 @@
         <v>156</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
@@ -5655,85 +5667,85 @@
         <v>372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="H9" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
@@ -5744,85 +5756,85 @@
         <v>259</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L13" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
@@ -5833,204 +5845,204 @@
         <v>295</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C16" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J18" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B19" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="D20" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J20" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="D21" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="D22" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E22" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H22" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="D23" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E23" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="H24" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I24" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J24" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -6053,103 +6065,103 @@
   <sheetData>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="4" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>351</v>
@@ -6158,202 +6170,202 @@
         <v>352</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="K7" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L7" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D8" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F8" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L8" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F10" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="K10" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L10" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N10" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D13" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E13" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F13" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D14" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E14" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B15" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D15" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E15" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -6375,91 +6387,91 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B11" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C11" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -6481,221 +6493,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B14" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -6712,246 +6724,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="J2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B27" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/地点（ちてん）.xlsx
+++ b/地点（ちてん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="方向（ほうこう）" sheetId="2" r:id="rId1"/>
@@ -38,12 +38,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="815">
   <si>
     <t>方位（ほうい）</t>
   </si>
   <si>
     <t>見当｜けんとう</t>
+  </si>
+  <si>
+    <t>針路｜しんろ</t>
   </si>
   <si>
     <t>上の</t>
@@ -1608,6 +1611,12 @@
   </si>
   <si>
     <t>（婚礼）</t>
+  </si>
+  <si>
+    <t>店舗</t>
+  </si>
+  <si>
+    <t>てんぽ</t>
   </si>
   <si>
     <t>交通機関</t>
@@ -3932,463 +3941,466 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:16">
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:16">
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4" s="1"/>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="F9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="H10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="C12" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="H16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:15">
       <c r="B17" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:15">
       <c r="B18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:15">
       <c r="B19" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:15">
       <c r="B20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:15">
       <c r="B21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:15">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:15">
       <c r="A23" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:15">
       <c r="A24" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4400,7 +4412,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
@@ -4420,1137 +4432,1145 @@
   <sheetData>
     <row r="1" ht="18" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N1" s="1"/>
       <c r="Q1" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:18">
       <c r="A3" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:18">
       <c r="A4" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:18">
       <c r="A5" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:18">
       <c r="A6" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O10" s="1"/>
     </row>
     <row r="11" ht="18" spans="1:18">
       <c r="A11" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:18">
       <c r="A12" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:18">
       <c r="A16" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:15">
       <c r="A17" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:15">
       <c r="A18" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:15">
       <c r="A19" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:15">
       <c r="A20" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:15">
       <c r="A21" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:15">
       <c r="A22" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:15">
       <c r="A23" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:15">
       <c r="A24" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:15">
       <c r="A25" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H25" s="1"/>
     </row>
     <row r="26" ht="18" spans="1:15">
       <c r="A26" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:15">
       <c r="A27" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:15">
       <c r="A28" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:15">
       <c r="A29" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:15">
       <c r="A30" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:15">
       <c r="A31" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:15">
       <c r="A32" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" ht="18" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C37" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G37" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" ht="18" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:7">
       <c r="A43" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="44" ht="18" spans="1:7">
       <c r="A44" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C44" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:7">
       <c r="A45" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C45" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="46" ht="18" spans="1:7">
       <c r="A46" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" ht="18" spans="1:7">
       <c r="A47" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E48" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F48" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:7">
       <c r="A49" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" ht="18" spans="1:7">
       <c r="A50" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E50" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F50" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" ht="18" spans="1:7">
       <c r="A51" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" ht="18" spans="1:7">
       <c r="A52" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:7">
       <c r="A53" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54" ht="18" spans="1:7">
       <c r="A54" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:7">
       <c r="A56" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:7">
       <c r="A57" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:7">
       <c r="A58" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C59" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C61" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C64" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C65" t="s">
-        <v>453</v>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>455</v>
+      </c>
+      <c r="B66" t="s">
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -5575,474 +5595,474 @@
   <sheetData>
     <row r="2" ht="18" spans="1:12">
       <c r="A2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="H3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
       <c r="A5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
       <c r="A6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
       <c r="A8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:12">
       <c r="A10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L10" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
       <c r="A13" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L13" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K14" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C15" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C16" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C17" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="J18" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:10">
       <c r="A19" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B19" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:10">
       <c r="D20" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="J20" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:10">
       <c r="D21" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:10">
       <c r="D22" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E22" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H22" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:10">
       <c r="D23" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="H24" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="I24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -6065,307 +6085,307 @@
   <sheetData>
     <row r="3" ht="18" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K3" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="O3" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="P3" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:16">
       <c r="A4" s="4" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="N4" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:16">
       <c r="A5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="K7" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L7" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E8" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="K8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="L8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F10" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K10" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="L10" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="N10" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E13" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F13" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D14" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E14" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B15" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D15" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E15" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -6387,91 +6407,91 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B11" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C11" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -6493,221 +6513,221 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B3" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B14" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -6724,246 +6744,246 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="J2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
       <c r="A4" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
       <c r="A6" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" ht="18" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:2">
       <c r="B26" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B27" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
